--- a/questionnaire_templates/002_aba_therapy_eligibility_screening--questionnaire_templates.xlsx
+++ b/questionnaire_templates/002_aba_therapy_eligibility_screening--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1026,8 +1026,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'male',_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Male', 'value': 'male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'female',_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Female', 'value': 'female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other/prefer_not_to_say',_'value':_'other'}</t>
+          <t>other/prefer_not_to_say</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other/Prefer not to say', 'value': 'other'}</t>
+          <t>Other/Prefer not to say</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'pending_evaluation',_'value':_'pending'}</t>
+          <t>pending_evaluation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Pending Evaluation', 'value': 'pending'}</t>
+          <t>Pending Evaluation</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'communication/speech',_'value':_'communication'}</t>
+          <t>communication/speech</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Communication/Speech', 'value': 'communication'}</t>
+          <t>Communication/Speech</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'social_skills',_'value':_'social_skills'}</t>
+          <t>social_skills</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Social Skills', 'value': 'social_skills'}</t>
+          <t>Social Skills</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'daily_living_skills',_'value':_'daily_living'}</t>
+          <t>daily_living_skills</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Daily Living Skills', 'value': 'daily_living'}</t>
+          <t>Daily Living Skills</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'aggression/behavioral_issues',_'value':_'aggression'}</t>
+          <t>aggression/behavioral_issues</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Aggression/Behavioral Issues', 'value': 'aggression'}</t>
+          <t>Aggression/Behavioral Issues</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'safety_concerns_(elopement)',_'value':_'safety'}</t>
+          <t>safety_concerns_(elopement)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Safety Concerns (Elopement)', 'value': 'safety'}</t>
+          <t>Safety Concerns (Elopement)</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'school_readiness',_'value':_'school_readiness'}</t>
+          <t>school_readiness</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'School Readiness', 'value': 'school_readiness'}</t>
+          <t>School Readiness</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'in-home',_'value':_'home'}</t>
+          <t>in-home</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'In-Home', 'value': 'home'}</t>
+          <t>In-Home</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'clinic-based',_'value':_'clinic'}</t>
+          <t>clinic-based</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Clinic-Based', 'value': 'clinic'}</t>
+          <t>Clinic-Based</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'school-based',_'value':_'school'}</t>
+          <t>school-based</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'School-Based', 'value': 'school'}</t>
+          <t>School-Based</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'telehealth',_'value':_'telehealth'}</t>
+          <t>telehealth</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Telehealth', 'value': 'telehealth'}</t>
+          <t>Telehealth</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'mornings_(8am_-_12pm)',_'value':_'morning'}</t>
+          <t>mornings_(8am_-_12pm)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Mornings (8am - 12pm)', 'value': 'morning'}</t>
+          <t>Mornings (8am - 12pm)</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'afternoons_(12pm_-_4pm)',_'value':_'afternoon'}</t>
+          <t>afternoons_(12pm_-_4pm)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoons (12pm - 4pm)', 'value': 'afternoon'}</t>
+          <t>Afternoons (12pm - 4pm)</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'late_afternoons_(4pm_-_6pm)',_'value':_'late_afternoon'}</t>
+          <t>late_afternoons_(4pm_-_6pm)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Late Afternoons (4pm - 6pm)', 'value': 'late_afternoon'}</t>
+          <t>Late Afternoons (4pm - 6pm)</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'pediatrician_referral',_'value':_'pediatrician'}</t>
+          <t>pediatrician_referral</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Pediatrician Referral', 'value': 'pediatrician'}</t>
+          <t>Pediatrician Referral</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'school_district',_'value':_'school'}</t>
+          <t>school_district</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'School District', 'value': 'school'}</t>
+          <t>School District</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'insurance_provider_list',_'value':_'insurance'}</t>
+          <t>insurance_provider_list</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Insurance Provider List', 'value': 'insurance'}</t>
+          <t>Insurance Provider List</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'online_search/social_media',_'value':_'online'}</t>
+          <t>online_search/social_media</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Online Search/Social Media', 'value': 'online'}</t>
+          <t>Online Search/Social Media</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'friend/family',_'value':_'friend_family'}</t>
+          <t>friend/family</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Friend/Family', 'value': 'friend_family'}</t>
+          <t>Friend/Family</t>
         </is>
       </c>
     </row>
